--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE_LUIS_BUSTAMANTE_Y_RIVERO</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>40204 NESTOR CACERES VELASQUEZ</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.43311</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.53865999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>379</v>
-      </c>
-      <c r="J2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.43311</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.53866</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40038 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.43316</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.526512</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1521</v>
-      </c>
-      <c r="J3" t="n">
-        <v>105</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.43316</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.526512</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>40121 EVERARDO ZAPATA SANTILLANA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.42333</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.53155</v>
-      </c>
-      <c r="I4" t="n">
-        <v>480</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.42333</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.53155</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40122 MANUEL SCORZA TORRES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.42536</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.5411</v>
-      </c>
-      <c r="I5" t="n">
-        <v>581</v>
-      </c>
-      <c r="J5" t="n">
-        <v>37</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.42536</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.5411</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.444814</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.514162</v>
-      </c>
-      <c r="I6" t="n">
-        <v>766</v>
-      </c>
-      <c r="J6" t="n">
-        <v>42</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.444814</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.514162</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>40631 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.449385</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.514318</v>
-      </c>
-      <c r="I7" t="n">
-        <v>213</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.449385</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.514318</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>41038 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.432588</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.53022799999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>271</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.432588</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.530228</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>7 DE AGOSTO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.42547</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.51575</v>
-      </c>
-      <c r="I9" t="n">
-        <v>399</v>
-      </c>
-      <c r="J9" t="n">
-        <v>29</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.42547</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.51575</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.426883</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.526922</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1084</v>
-      </c>
-      <c r="J10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.426883</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.526922</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.44493</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.51514</v>
-      </c>
-      <c r="I11" t="n">
-        <v>206</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.44493</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.51514</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>COLEGIO PARTICULAR MIXTO SANTA CLARA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.43292</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.53283</v>
-      </c>
-      <c r="I12" t="n">
-        <v>915</v>
-      </c>
-      <c r="J12" t="n">
-        <v>66</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.43292</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.53283</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>PERUANO SUIZO ALFRED WERNER</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.42338</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.53233</v>
-      </c>
-      <c r="I13" t="n">
-        <v>219</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.42338</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.53233</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>PAMER AREQUIPA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.43005</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.52333</v>
-      </c>
-      <c r="I14" t="n">
-        <v>331</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.43005</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.52333</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>MADRE SANTA BEATRIZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.429242</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.517082</v>
-      </c>
-      <c r="I15" t="n">
-        <v>317</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.429242</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.517082</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>SANTA MARIA MADRE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.42401</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.5194</v>
-      </c>
-      <c r="I16" t="n">
-        <v>237</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.42401</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.5194</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SANTA URSULA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.43085</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.52041</v>
-      </c>
-      <c r="I17" t="n">
-        <v>699</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.43085</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.52041</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>MAGISTER LAGRANGE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.41697</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.53051000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>294</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.41697</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.53051</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>41006 JORGE POLAR</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.426769</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.521057</v>
-      </c>
-      <c r="I19" t="n">
-        <v>435</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.426769</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.521057</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>WINNIE</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.43021</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.52646</v>
-      </c>
-      <c r="I20" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.43021</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.52646</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>ILLARY</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.43446</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.52934</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.43446</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.52934</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>WOLFANG AMADEUS MOZART</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.435121</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.526034</v>
-      </c>
-      <c r="I22" t="n">
-        <v>368</v>
-      </c>
-      <c r="J22" t="n">
-        <v>24</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.435121</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.526034</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>VECTOR</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.42613</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.53436000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>224</v>
-      </c>
-      <c r="J23" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.42613</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.53436</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>GOTITAS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.43026</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.52752</v>
-      </c>
-      <c r="I24" t="n">
-        <v>31</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.43026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.52752</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>MUNDO ECOLOGICO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.42842</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.52213</v>
-      </c>
-      <c r="I25" t="n">
-        <v>200</v>
-      </c>
-      <c r="J25" t="n">
-        <v>26</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.42842</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.52213</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>FUTURA SCHOOLS JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.44158</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.52458</v>
-      </c>
-      <c r="I26" t="n">
-        <v>704</v>
-      </c>
-      <c r="J26" t="n">
-        <v>32</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.44158</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.52458</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>MATER MARIA SCHOOL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.430081</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.54059100000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>22</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.430081</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.540591</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>INNOVA SCHOOLS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.43852</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.50798</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1261</v>
-      </c>
-      <c r="J28" t="n">
-        <v>53</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.43852</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.50798</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.43451</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.52119999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>212</v>
-      </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.43451</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.5212</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>64054</t>
+          <t>536308</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40204 NESTOR CACERES VELASQUEZ</t>
+          <t>ILLARY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.43311</t>
+          <t>-16.43446</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.53866</t>
+          <t>-71.52934</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>65652</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40121 EVERARDO ZAPATA SANTILLANA</t>
+          <t>40631 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.42333</t>
+          <t>-16.449385</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.53155</t>
+          <t>-71.514318</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40122 MANUEL SCORZA TORRES</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.42536</t>
+          <t>-16.44493</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.5411</t>
+          <t>-71.51514</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
+          <t>41038 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.444814</t>
+          <t>-16.432588</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.514162</t>
+          <t>-71.530228</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>65652</t>
+          <t>66166</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40631 JUAN PABLO II</t>
+          <t>SANTA MARIA MADRE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.449385</t>
+          <t>-16.42401</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.514318</t>
+          <t>-71.5194</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>65666</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41038 JOSE OLAYA BALANDRA</t>
+          <t>MAGISTER LAGRANGE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.432588</t>
+          <t>-16.41697</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.530228</t>
+          <t>-71.53051</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>65671</t>
+          <t>586256</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7 DE AGOSTO</t>
+          <t>VECTOR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.42547</t>
+          <t>-16.42613</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.51575</t>
+          <t>-71.53436</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>802991</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.426883</t>
+          <t>-16.43451</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.526922</t>
+          <t>-71.5212</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>65789</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>PERUANO SUIZO ALFRED WERNER</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.44493</t>
+          <t>-16.42338</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.51514</t>
+          <t>-71.53233</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>533381</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COLEGIO PARTICULAR MIXTO SANTA CLARA</t>
+          <t>WINNIE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.43292</t>
+          <t>-16.43021</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.53283</t>
+          <t>-71.52646</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>66147</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO ALFRED WERNER</t>
+          <t>MADRE SANTA BEATRIZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.42338</t>
+          <t>-16.429242</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.53233</t>
+          <t>-71.517082</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>120192</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MADRE SANTA BEATRIZ</t>
+          <t>41006 JORGE POLAR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.429242</t>
+          <t>-16.426769</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.517082</t>
+          <t>-71.521057</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>551600</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANTA MARIA MADRE</t>
+          <t>WOLFANG AMADEUS MOZART</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.42401</t>
+          <t>-16.435121</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.5194</t>
+          <t>-71.526034</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>66190</t>
+          <t>649857</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA URSULA</t>
+          <t>MUNDO ECOLOGICO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.43085</t>
+          <t>-16.42842</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.52041</t>
+          <t>-71.52213</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>66388</t>
+          <t>64054</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MAGISTER LAGRANGE</t>
+          <t>40204 NESTOR CACERES VELASQUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.41697</t>
+          <t>-16.43311</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.53051</t>
+          <t>-71.53866</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>120192</t>
+          <t>65671</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41006 JORGE POLAR</t>
+          <t>7 DE AGOSTO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.426769</t>
+          <t>-16.42547</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.521057</t>
+          <t>-71.51575</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>399</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>533381</t>
+          <t>646934</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WINNIE</t>
+          <t>GOTITAS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.43021</t>
+          <t>-16.43026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.52646</t>
+          <t>-71.52752</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>536308</t>
+          <t>65586</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ILLARY</t>
+          <t>40121 EVERARDO ZAPATA SANTILLANA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.43446</t>
+          <t>-16.42333</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.52934</t>
+          <t>-71.53155</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>551600</t>
+          <t>723507</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WOLFANG AMADEUS MOZART</t>
+          <t>FUTURA SCHOOLS JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.435121</t>
+          <t>-16.44158</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.526034</t>
+          <t>-71.52458</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>704</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>586256</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VECTOR</t>
+          <t>40122 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.42613</t>
+          <t>-16.42536</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.53436</t>
+          <t>-71.5411</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>581</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>646934</t>
+          <t>65633</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GOTITAS</t>
+          <t>40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.43026</t>
+          <t>-16.444814</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.52752</t>
+          <t>-71.514162</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>766</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>649857</t>
+          <t>781700</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MUNDO ECOLOGICO</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.42842</t>
+          <t>-16.43852</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.52213</t>
+          <t>-71.50798</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>723507</t>
+          <t>66190</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>SANTA URSULA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.44158</t>
+          <t>-16.43085</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.52458</t>
+          <t>-71.52041</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>699</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>781700</t>
+          <t>65732</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.43852</t>
+          <t>-16.426883</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.50798</t>
+          <t>-71.526922</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>802991</t>
+          <t>65812</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>COLEGIO PARTICULAR MIXTO SANTA CLARA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.43451</t>
+          <t>-16.43292</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.5212</t>
+          <t>-71.53283</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>915</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>536308</t>
+          <t>802991</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ILLARY</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.43446</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.52934</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.43451</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-71.5212</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>781700</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40038 JORGE BASADRE GROHMANN</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.43316</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.526512</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>-16.43852</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>-71.50798</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65652</t>
+          <t>781309</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40631 JUAN PABLO II</t>
+          <t>MATER MARIA SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.449385</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.514318</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-16.430081</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.540591</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65789</t>
+          <t>723507</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>FUTURA SCHOOLS JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.44493</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.51514</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-16.44158</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.52458</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>65666</t>
+          <t>649857</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41038 JOSE OLAYA BALANDRA</t>
+          <t>MUNDO ECOLOGICO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.432588</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.530228</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-16.42842</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.52213</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>646934</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SANTA MARIA MADRE</t>
+          <t>GOTITAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.42401</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.5194</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-16.43026</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.52752</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66388</t>
+          <t>586256</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MAGISTER LAGRANGE</t>
+          <t>VECTOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.41697</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.53051</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-16.42613</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.53436</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>586256</t>
+          <t>551600</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VECTOR</t>
+          <t>WOLFANG AMADEUS MOZART</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.42613</t>
+          <t>368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.53436</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-16.435121</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.526034</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>802991</t>
+          <t>536308</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>ILLARY</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.43451</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.5212</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-16.43446</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.52934</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>533381</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO ALFRED WERNER</t>
+          <t>WINNIE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.42338</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.53233</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-16.43021</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.52646</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>533381</t>
+          <t>120192</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WINNIE</t>
+          <t>41006 JORGE POLAR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.43021</t>
+          <t>435</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.52646</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-16.426769</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-71.521057</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>066388</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MADRE SANTA BEATRIZ</t>
+          <t>MAGISTER LAGRANGE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.429242</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.517082</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-16.41697</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.53051</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>66109</t>
+          <t>066190</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PAMER AREQUIPA</t>
+          <t>SANTA URSULA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.43005</t>
+          <t>699</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.52333</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-16.43085</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.52041</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>120192</t>
+          <t>066166</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41006 JORGE POLAR</t>
+          <t>SANTA MARIA MADRE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.426769</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.521057</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>-16.42401</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.5194</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>551600</t>
+          <t>066147</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WOLFANG AMADEUS MOZART</t>
+          <t>MADRE SANTA BEATRIZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.435121</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.526034</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-16.429242</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-71.517082</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>649857</t>
+          <t>066109</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MUNDO ECOLOGICO</t>
+          <t>PAMER AREQUIPA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.42842</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.52213</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-16.43005</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.52333</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>64054</t>
+          <t>066086</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40204 NESTOR CACERES VELASQUEZ</t>
+          <t>PERUANO SUIZO ALFRED WERNER</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.43311</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.53866</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-16.42338</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.53233</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65671</t>
+          <t>065812</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7 DE AGOSTO</t>
+          <t>COLEGIO PARTICULAR MIXTO SANTA CLARA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.42547</t>
+          <t>915</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.51575</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-16.43292</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.53283</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>646934</t>
+          <t>065789</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GOTITAS</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.43026</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.52752</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-16.44493</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-71.51514</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>065732</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40121 EVERARDO ZAPATA SANTILLANA</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.42333</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.53155</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-16.426883</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.526922</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>723507</t>
+          <t>065671</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>7 DE AGOSTO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.44158</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.52458</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>-16.42547</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.51575</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>065666</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40122 MANUEL SCORZA TORRES</t>
+          <t>41038 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.42536</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.5411</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>-16.432588</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.530228</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>065652</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
+          <t>40631 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.444814</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.514162</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>-16.449385</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-71.514318</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>781700</t>
+          <t>065633</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.43852</t>
+          <t>766</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.50798</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>-16.444814</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-71.514162</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>66190</t>
+          <t>065591</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA URSULA</t>
+          <t>40122 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.43085</t>
+          <t>581</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.52041</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>-16.42536</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-71.5411</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>781309</t>
+          <t>065586</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MATER MARIA SCHOOL</t>
+          <t>40121 EVERARDO ZAPATA SANTILLANA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.430081</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.540591</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-16.42333</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-71.53155</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>065572</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>40038 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.426883</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.526922</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>-16.43316</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-71.526512</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>064054</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COLEGIO PARTICULAR MIXTO SANTA CLARA</t>
+          <t>40204 NESTOR CACERES VELASQUEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.43292</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.53283</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>-16.43311</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-71.53866</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-JOSE_LUIS_BUSTAMANTE_Y_RIVERO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
